--- a/bangluudulieu_tamthoi.xlsx
+++ b/bangluudulieu_tamthoi.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39.140625" customWidth="1" min="1" max="1"/>
@@ -464,7 +464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>43H06592</t>
+          <t>43C01338_C</t>
         </is>
       </c>
     </row>
@@ -496,17 +496,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>43C05815_C</t>
+          <t>43C11608_C</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>43C05815_C</t>
+          <t>43C11608_C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43C05815_C</t>
+          <t>43C11608_C</t>
         </is>
       </c>
     </row>
@@ -518,17 +518,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:19:09 02/07/2024</t>
+          <t>09:15:17 17/07/2024</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>09:18:09 02/07/2024</t>
+          <t>09:14:57 17/07/2024</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:15</t>
         </is>
       </c>
     </row>
@@ -539,16 +539,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>34   km/h</t>
+          <t>26   km/h</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -559,11 +559,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>36   km/h</t>
+          <t>24   km/h</t>
         </is>
       </c>
     </row>
@@ -574,16 +574,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87.3809</v>
+        <v>8.963200000000001</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>85.24  km</t>
+          <t>8.96  km</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>8.96</t>
         </is>
       </c>
     </row>
@@ -594,11 +594,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19 lần</t>
+          <t>4 lần</t>
         </is>
       </c>
     </row>
@@ -639,17 +639,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hùng Vương, X. Duy Sơn, H. Duy Xuyên, Quảng Nam</t>
+          <t>Ngô Quyền, P. An Hải Đông, Q. Sơn Trà, TP. Đà Nẵng</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hùng Vương, X. Duy Trung, H. Duy Xuyên, Quảng Nam</t>
+          <t>Ngô Quyền, P. An Hải Tây, Q. Sơn Trà, TP. Đà Nẵng</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hùng Vương, X. Duy Trung, H. Duy Xuyên, Quảng Nam</t>
+          <t>Ngô Quyền, P. An Hải Tây, Q. Sơn Trà, TP. Đà Nẵng</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -672,11 +672,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>270</v>
+        <v>136</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  270L</t>
+          <t xml:space="preserve">  136L</t>
         </is>
       </c>
     </row>
@@ -700,12 +700,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0905266552</t>
+          <t>905610374</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0905266552</t>
+          <t>905610374</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LE VUONG</t>
+          <t>PHAN VAN THANG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LE VUONG</t>
+          <t>PHAN VAN THANG</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LE VUONG</t>
+          <t>PHAN VAN THANG</t>
         </is>
       </c>
     </row>
@@ -739,17 +739,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>480122481248</t>
+          <t>620135004685</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>480122481248</t>
+          <t>620135004685</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>480122481248</t>
+          <t>620135004685</t>
         </is>
       </c>
     </row>
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>124 phút</t>
+          <t>19 phút</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -780,16 +780,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>174</v>
+        <v>19</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>171 phút</t>
+          <t>19 phút</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Xe đến hạn thu phí dịch vụ ngày: 01/07/2025</t>
+          <t>Xe đến hạn thu phí dịch vụ ngày: 01/05/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Xe đến hạn thu phí dịch vụ ngày: 01/07/2025</t>
+          <t>Xe đến hạn thu phí dịch vụ ngày: 01/05/2025</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SCVINAQCB010</t>
+          <t>SCVTQC030</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vina</t>
+          <t>Viettel</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10240 (MB)</t>
+          <t>30720 (MB)</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Click vào checkbox "Hiển thị nhiên liệu"</t>
+          <t>Mở chức năng "Báo cáo vi phạm lái xe"</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hiển thị thêm trường "N/Liệu" ở danh sách lộ trình</t>
+          <t>Chuyển tới trang GPS V3 module "Báo cáo xếp hạng lái xe"</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://gps.binhanh.vn/publicData/Report/SystemVehicleStatus/hien_trang_he_thong_43E02740_2024_07_02_09_07_23.xlsx</t>
+          <t>https://gps.binhanh.vn/publicData/Report/SystemVehicleStatus/hien_trang_he_thong_43E02740_2024_07_17_09_03_39.xlsx</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10:50:42</t>
+          <t>10:04:07</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,38 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>truongtest2990474</t>
+          <t>truongtest3606679</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>biển số</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>43C06120_C</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>time update 1p</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>05:10:07 17/07/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>số lần cập nhật</t>
         </is>
       </c>
     </row>
